--- a/HW5/HW5.xlsx
+++ b/HW5/HW5.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{352F90F9-866C-49E6-B0C9-DA733BF1AE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9160" yWindow="0" windowWidth="15520" windowHeight="16000" xr2:uid="{FE28BE45-CC51-4C8B-A10B-4C5C8BD2FEEC}"/>
+    <workbookView xWindow="380" yWindow="0" windowWidth="15520" windowHeight="16000" activeTab="1" xr2:uid="{FE28BE45-CC51-4C8B-A10B-4C5C8BD2FEEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of Contents" sheetId="2" r:id="rId1"/>
